--- a/S26_영웅명세/contribution_rankings.xlsx
+++ b/S26_영웅명세/contribution_rankings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hippo\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hippo\OneDrive\Escritorio\새 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08180E5-86CB-4946-9817-AA0472092F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC8D3BF-3BEE-4F68-910E-FAD7FD1A24FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="90" windowWidth="30615" windowHeight="20790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="703">
   <si>
     <t>랭킹</t>
   </si>
@@ -2113,6 +2113,46 @@
   </si>
   <si>
     <t>맹원 계</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in100</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in200</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in300</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in400</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in500</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in600</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>in700</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>점유율</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>점유율 계</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2281,7 +2321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2461,8 +2501,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2574,6 +2626,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2706,8 +2773,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3084,28 +3163,31 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="G1">
-        <v>100</v>
-      </c>
-      <c r="H1">
-        <v>200</v>
-      </c>
-      <c r="I1">
-        <v>300</v>
-      </c>
-      <c r="J1">
-        <v>400</v>
-      </c>
-      <c r="K1">
-        <v>500</v>
-      </c>
-      <c r="L1">
-        <v>600</v>
-      </c>
-      <c r="M1">
+      <c r="F1" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="N1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>692</v>
       </c>
     </row>
@@ -3122,38 +3204,38 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2">
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3">
         <f>COUNTIF($D$2:$D$101,$F2)</f>
         <v>81</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <f>COUNTIF($D$102:$D$201,$F2)</f>
         <v>53</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="3">
         <f>COUNTIF($D$202:$D$301,$F2)</f>
         <v>34</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="3">
         <f>COUNTIF($D$302:$D$401,$F2)</f>
         <v>18</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="3">
         <f>COUNTIF($D$402:$D$501,$F2)</f>
         <v>10</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="3">
         <f>COUNTIF($D$502:$D$601,$F2)</f>
         <v>3</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="3">
         <f>COUNTIF($D$602:$D$700,$F2)</f>
         <v>0</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="3">
         <f>SUM(G2:M2)</f>
         <v>199</v>
       </c>
@@ -3171,39 +3253,39 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="3">
         <f t="shared" ref="G3:G6" si="0">COUNTIF($D$2:$D$101,$F3)</f>
         <v>17</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <f t="shared" ref="H3:H6" si="1">COUNTIF($D$102:$D$201,$F3)</f>
         <v>38</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <f t="shared" ref="I3:I6" si="2">COUNTIF($D$202:$D$301,$F3)</f>
         <v>52</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <f t="shared" ref="J3:J6" si="3">COUNTIF($D$302:$D$401,$F3)</f>
         <v>44</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="3">
         <f t="shared" ref="K3:K6" si="4">COUNTIF($D$402:$D$501,$F3)</f>
         <v>26</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="3">
         <f t="shared" ref="L3:L6" si="5">COUNTIF($D$502:$D$601,$F3)</f>
         <v>13</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="3">
         <f t="shared" ref="M3:M6" si="6">COUNTIF($D$602:$D$700,$F3)</f>
         <v>9</v>
       </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N6" si="7">SUM(G3:M3)</f>
+      <c r="N3" s="3">
+        <f t="shared" ref="N3:N7" si="7">SUM(G3:M3)</f>
         <v>199</v>
       </c>
     </row>
@@ -3220,38 +3302,38 @@
       <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="3">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="3">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="3">
         <f t="shared" si="5"/>
         <v>68</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="3">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="3">
         <f t="shared" si="7"/>
         <v>198</v>
       </c>
@@ -3269,38 +3351,38 @@
       <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="3">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="3">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="3">
         <f t="shared" si="6"/>
         <v>48</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="3">
         <f t="shared" si="7"/>
         <v>68</v>
       </c>
@@ -3318,38 +3400,38 @@
       <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="3">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="3">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="3">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
@@ -3366,6 +3448,33 @@
       </c>
       <c r="D7" t="s">
         <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -3381,6 +3490,41 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4">
+        <f>G2/100</f>
+        <v>0.81</v>
+      </c>
+      <c r="H8" s="4">
+        <f>H2/100</f>
+        <v>0.53</v>
+      </c>
+      <c r="I8" s="4">
+        <f>I2/100</f>
+        <v>0.34</v>
+      </c>
+      <c r="J8" s="4">
+        <f>J2/100</f>
+        <v>0.18</v>
+      </c>
+      <c r="K8" s="4">
+        <f>K2/100</f>
+        <v>0.1</v>
+      </c>
+      <c r="L8" s="4">
+        <f>L2/100</f>
+        <v>0.03</v>
+      </c>
+      <c r="M8" s="4">
+        <f>M2/100</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <f>SUM(G8:M8)/6.76</f>
+        <v>0.29437869822485213</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -3395,6 +3539,41 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="4">
+        <f>G3/100</f>
+        <v>0.17</v>
+      </c>
+      <c r="H9" s="4">
+        <f>H3/100</f>
+        <v>0.38</v>
+      </c>
+      <c r="I9" s="4">
+        <f>I3/100</f>
+        <v>0.52</v>
+      </c>
+      <c r="J9" s="4">
+        <f>J3/100</f>
+        <v>0.44</v>
+      </c>
+      <c r="K9" s="4">
+        <f>K3/100</f>
+        <v>0.26</v>
+      </c>
+      <c r="L9" s="4">
+        <f>L3/100</f>
+        <v>0.13</v>
+      </c>
+      <c r="M9" s="4">
+        <f>M3/100</f>
+        <v>0.09</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" ref="N9:N12" si="8">SUM(G9:M9)/6.76</f>
+        <v>0.29437869822485208</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -3408,6 +3587,41 @@
       </c>
       <c r="D10" t="s">
         <v>5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="4">
+        <f>G4/100</f>
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="4">
+        <f>H4/100</f>
+        <v>0.09</v>
+      </c>
+      <c r="I10" s="4">
+        <f>I4/100</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J10" s="4">
+        <f>J4/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="K10" s="4">
+        <f>K4/100</f>
+        <v>0.6</v>
+      </c>
+      <c r="L10" s="4">
+        <f>L4/100</f>
+        <v>0.68</v>
+      </c>
+      <c r="M10" s="4">
+        <f>M4/100</f>
+        <v>0.08</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="8"/>
+        <v>0.29289940828402367</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -3423,6 +3637,41 @@
       <c r="D11" t="s">
         <v>5</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="4">
+        <f>G5/100</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <f>H5/100</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <f>I5/100</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <f>J5/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="4">
+        <f>K5/100</f>
+        <v>0.04</v>
+      </c>
+      <c r="L11" s="4">
+        <f>L5/100</f>
+        <v>0.15</v>
+      </c>
+      <c r="M11" s="4">
+        <f>M5/100</f>
+        <v>0.48</v>
+      </c>
+      <c r="N11" s="4">
+        <f t="shared" si="8"/>
+        <v>0.10059171597633136</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -3436,6 +3685,41 @@
       </c>
       <c r="D12" t="s">
         <v>5</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="4">
+        <f>G6/100</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <f>H6/100</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <f>I6/100</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <f>J6/100</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <f>K6/100</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <f>L6/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="M12" s="4">
+        <f>M6/100</f>
+        <v>0.11</v>
+      </c>
+      <c r="N12" s="4">
+        <f t="shared" si="8"/>
+        <v>1.7751479289940829E-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -12752,5 +13036,6 @@
   <autoFilter ref="A1:D677" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>